--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bc190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a238b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bc490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a24070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a02f40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bca60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a02af0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888c0fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bcf10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a24dc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d82e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2f40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2dc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888c5eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2cd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2e80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888c51f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bc190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888811280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a24610&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a24190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bcca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bc700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888875910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bcf10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888875d90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a64fa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a7ce80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98899bd0a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98899bd1f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a7cb20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a15700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a7c700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a7cee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a647f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98899bda60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a24070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880eaf310&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dc220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dcd00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dcb80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dc5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dc0d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dcc10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dc2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888899ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888899eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a02820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a026d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880eafaf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880eaf280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880eaf340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888fa280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888fae80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888fac40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a17f10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888fa850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98885471f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882682b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98885478e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888547790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888547ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880eafe80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a31100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880eaf8b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888899970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888268280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854b220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888546e50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854b5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854b940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854bcd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888547cd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888547730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888faa90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a6f940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98887d58e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888a3e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b93d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b96d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9df0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888faca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a6ffa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854bd60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854b400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888547790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888a3790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888a3910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9310&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888c77f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854b5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888a38b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb2400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb27f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb2b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb2ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb42e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888875a90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889acb4f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889ad11f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988889c340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a01490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dc160&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880e9d6d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880e9d850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880e9de50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a8aa00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988889c4c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880e9dd90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880e9d8b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb4a90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb44f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bc190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a238b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bc490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a24070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a02f40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bca60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a02af0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888c0fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bcf10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a24dc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2be0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d82e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2f40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2dc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888c5eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2cd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888d2e80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888c51f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bc190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888811280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a24610&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a24190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bcca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bc700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888875910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888bcf10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888875d90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a64fa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a7ce80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98899bd0a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98899bd1f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a7cb20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a15700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a7c700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a7cee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a647f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98899bda60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a24070&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880eaf310&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dc220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dcd00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dcb80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dc5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dc0d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dcc10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dc2e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888899ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888899eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a02820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a026d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880eafaf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880eaf280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880eaf340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888fa280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888fae80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888fac40&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a17f10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888fa850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98885471f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882682b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98885478e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888547790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888547ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880eafe80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a31100&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880eaf8b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888899970&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888268280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854b220&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888546e50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854b5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854b940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854bcd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888547cd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888547730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888faa90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a6f940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98887d58e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888a3e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b93d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b96d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9df0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888faca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a6ffa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854bd60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854b400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888547790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888a3790&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888a3910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9310&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888c77f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888b9d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988854b5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98888a38b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb2400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb27f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb2b80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb2ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb42e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9888875a90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889acb4f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889ad11f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988889c340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a01490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f98882dc160&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880e9d6d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880e9d850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880e9de50&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9889a8aa00&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f988889c4c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880e9dd90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880e9d8b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb4a90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f9880fb44f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc54580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd3b190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc541c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd682e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc543d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc54e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd3a0d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd21430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd2d880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd2dfa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbe3700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbe3670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbe3280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbee1f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbe3ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbee340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbde1f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd48b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd3b2b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbde040&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbd9ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd94d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbd9a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbd9f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbd9eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb28310&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd2df10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd94b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb8c880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbd9910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd949d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb8c910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb8c520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd7bc70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb8cd90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc54f10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc54250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb8c1c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc54eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc54820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec14ab20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec14a640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec207ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec14ad60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec14a430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd7c0a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd3a730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd21490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd483d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd21880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc119a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc115e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11c70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd65190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd65520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11160&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec422eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec425b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec425400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec425d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec425610&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd3aa30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edce11c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd65f10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb9d190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec2076d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42a250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42a5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42acd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42aac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42afd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edce3af0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec426250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec41dcd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec14ddc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec4225b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5baee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59be80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59b3d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59b760&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59bc70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec422850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd86a30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42a400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42a0a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42afa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5ba310&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5baaf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd7c7c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5ba8b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59b7f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5bab80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5ba4f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5ba730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5bab20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca38460&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca38880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca38f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca16370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca38c10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eddc7430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb9d4c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59b130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59b580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec96faf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec6fb580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec6fb9a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec14de80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec6fbd30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5c1430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ede49fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca388e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca38940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eddc7430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec43b5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc54580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd3b190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc541c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd682e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc543d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc54e20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd3a0d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd21430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd2d880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd2dfa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbe3700&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbe3670&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbe3280&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbee1f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbe3ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbee340&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbde1f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd48b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd3b2b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbde040&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbd9ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd94d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbd9a60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbd9f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbd9eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb28310&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd2df10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd94b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb8c880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecbd9910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd949d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb8c910&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb8c520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd7bc70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb8cd90&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc54f10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc54250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb8c1c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc54eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edc54820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec14ab20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec14a640&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec207ee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec14ad60&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec14a430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd7c0a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd3a730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd21490&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd483d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd21880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc119a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc115e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11820&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11c70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd65190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd65520&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11160&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11ca0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec422eb0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec425b20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec425400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec425d30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec425610&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd3aa30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edce11c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd65f10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb9d190&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec2076d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42a250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42a5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42acd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42aac0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42afd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edce3af0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec426250&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec41dcd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec14ddc0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec4225b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5baee0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59be80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59b3d0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59b760&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59bc70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec422850&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd86a30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecc11130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42a400&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42a0a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec42afa0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5ba310&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5baaf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56edd7c7c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5ba8b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59b7f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5bab80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5ba4f0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5ba730&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5bab20&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca38460&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca38880&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca38f70&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca16370&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca38c10&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eddc7430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ecb9d4c0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59b130&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec59b580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec96faf0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec6fb580&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec6fb9a0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec14de80&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec6fbd30&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec5c1430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ede49fd0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca388e0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eca38940&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56eddc7430&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='rte.orpgujarat.com', port=443) at 0x7f56ec43b5b0&gt;, 'Connection to rte.orpgujarat.com timed out. (connect timeout=15)'))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
+          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">

--- a/RTE_Status_Results.xlsx
+++ b/RTE_Status_Results.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N94" s="9" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N95" s="9" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N109" s="9" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N117" s="9" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N118" s="9" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N137" s="9" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N140" s="9" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N141" s="9" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N147" s="9" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N154" s="9" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N158" s="9" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N159" s="9" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N170" s="9" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N171" s="9" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N176" s="9" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N177" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N180" s="9" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N193" s="9" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N195" s="9" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="M206" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N206" s="9" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="M212" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N212" s="9" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="M213" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N213" s="9" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M221" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N221" s="9" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N237" s="9" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="M240" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N240" s="9" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="M245" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N245" s="9" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M247" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N247" s="9" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="M252" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N252" s="9" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="M253" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N253" s="9" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="M260" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N260" s="9" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="M268" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N268" s="9" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="M272" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N272" s="9" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="M288" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N288" s="9" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="M293" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N293" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="M298" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N298" s="9" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="M302" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N302" s="9" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="M303" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N303" s="9" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M312" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N312" s="9" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="M316" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N316" s="9" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="M317" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N317" s="9" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M318" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N318" s="9" t="inlineStr">
@@ -21845,7 +21845,7 @@
       </c>
       <c r="M324" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N324" s="9" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="M337" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N337" s="9" t="inlineStr">
@@ -22897,7 +22897,7 @@
       </c>
       <c r="M340" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N340" s="9" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="M345" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N345" s="9" t="inlineStr">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="M349" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N349" s="9" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="M353" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N353" s="9" t="inlineStr">
@@ -23821,7 +23821,7 @@
       </c>
       <c r="M354" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N354" s="9" t="inlineStr">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="M369" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N369" s="9" t="inlineStr">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="M378" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N378" s="9" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="M379" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N379" s="9" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="M380" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N380" s="9" t="inlineStr">
@@ -26589,7 +26589,7 @@
       </c>
       <c r="M396" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N396" s="9" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="M399" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N399" s="9" t="inlineStr">
@@ -26853,7 +26853,7 @@
       </c>
       <c r="M400" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N400" s="9" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="M401" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N401" s="9" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="M403" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N403" s="9" t="inlineStr">
@@ -27117,7 +27117,7 @@
       </c>
       <c r="M404" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N404" s="9" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="M405" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N405" s="9" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="M406" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N406" s="9" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="M407" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N407" s="9" t="inlineStr">
@@ -28103,7 +28103,7 @@
       </c>
       <c r="M419" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N419" s="9" t="inlineStr">
@@ -29027,7 +29027,7 @@
       </c>
       <c r="M433" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N433" s="9" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="M434" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N434" s="9" t="inlineStr">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="M435" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N435" s="9" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="M442" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N442" s="9" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="M449" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N449" s="9" t="inlineStr">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="M457" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N457" s="9" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="M461" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N461" s="9" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="M465" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N465" s="9" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="M468" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N468" s="9" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="M469" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N469" s="9" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="M480" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N480" s="9" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M482" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N482" s="9" t="inlineStr">
@@ -32319,7 +32319,7 @@
       </c>
       <c r="M483" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N483" s="9" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="M487" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N487" s="9" t="inlineStr">
@@ -32913,7 +32913,7 @@
       </c>
       <c r="M492" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N492" s="9" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="M505" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N505" s="9" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="M518" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N518" s="9" t="inlineStr">
@@ -35241,7 +35241,7 @@
       </c>
       <c r="M527" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N527" s="9" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="M531" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N531" s="9" t="inlineStr">
@@ -35765,7 +35765,7 @@
       </c>
       <c r="M535" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N535" s="9" t="inlineStr">
@@ -36291,7 +36291,7 @@
       </c>
       <c r="M543" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N543" s="9" t="inlineStr">
@@ -36949,7 +36949,7 @@
       </c>
       <c r="M553" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N553" s="9" t="inlineStr">
@@ -37213,7 +37213,7 @@
       </c>
       <c r="M557" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N557" s="9" t="inlineStr">
@@ -37675,7 +37675,7 @@
       </c>
       <c r="M564" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N564" s="9" t="inlineStr">
@@ -37873,7 +37873,7 @@
       </c>
       <c r="M567" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N567" s="9" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="M579" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N579" s="9" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="M588" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N588" s="9" t="inlineStr">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="M609" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N609" s="9" t="inlineStr">
@@ -40971,7 +40971,7 @@
       </c>
       <c r="M614" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N614" s="9" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="M646" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N646" s="9" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M653" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N653" s="9" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="M657" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N657" s="9" t="inlineStr">
@@ -43937,7 +43937,7 @@
       </c>
       <c r="M659" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N659" s="9" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="M667" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N667" s="9" t="inlineStr">
@@ -45113,7 +45113,7 @@
       </c>
       <c r="M677" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N677" s="9" t="inlineStr">
@@ -45245,7 +45245,7 @@
       </c>
       <c r="M679" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N679" s="9" t="inlineStr">
@@ -45509,7 +45509,7 @@
       </c>
       <c r="M683" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N683" s="9" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="M685" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N685" s="9" t="inlineStr">
@@ -45707,7 +45707,7 @@
       </c>
       <c r="M686" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N686" s="9" t="inlineStr">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="M688" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N688" s="9" t="inlineStr">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="M690" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N690" s="9" t="inlineStr">
@@ -46037,7 +46037,7 @@
       </c>
       <c r="M691" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N691" s="9" t="inlineStr">
@@ -46293,7 +46293,7 @@
       </c>
       <c r="M695" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N695" s="9" t="inlineStr">
@@ -47137,7 +47137,7 @@
       </c>
       <c r="M708" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N708" s="9" t="inlineStr">
@@ -47269,7 +47269,7 @@
       </c>
       <c r="M710" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N710" s="9" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="M711" s="8" t="inlineStr">
         <is>
-          <t>ERROR: HTTPSConnectionPool(host='rte.orpgujarat.com', port=443): Max retries exceeded with url: /ApplicationFormStatus (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate has expired (_ssl.c:1147)')))</t>
+          <t>ERROR: 503 Server Error: Service Unavailable for url: https://rte.orpgujarat.com/ApplicationFormStatus</t>
         </is>
       </c>
       <c r="N711" s="9" t="inlineStr">
